--- a/employee_information_forms/047_employee_assistance_program_access_request_form--employee_information_forms.xlsx
+++ b/employee_information_forms/047_employee_assistance_program_access_request_form--employee_information_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'counseling'}</t>
+          <t>counseling</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Counseling'}</t>
+          <t>Counseling</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'financial_planning'}</t>
+          <t>financial_planning</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Financial Planning'}</t>
+          <t>Financial Planning</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'legal_support'}</t>
+          <t>legal_support</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Legal Support'}</t>
+          <t>Legal Support</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'leave_of_absence'}</t>
+          <t>leave_of_absence</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Leave of Absence'}</t>
+          <t>Leave of Absence</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'retired'}</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Retired'}</t>
+          <t>Retired</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'approve'}</t>
+          <t>approve</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Approve'}</t>
+          <t>Approve</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'reject'}</t>
+          <t>reject</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Reject'}</t>
+          <t>Reject</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
